--- a/artfynd/A 15984-2026 artfynd.xlsx
+++ b/artfynd/A 15984-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132532684</v>
+        <v>132533434</v>
       </c>
       <c r="B2" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582295</v>
+        <v>582221</v>
       </c>
       <c r="R2" t="n">
-        <v>7043428</v>
+        <v>7043494</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132533434</v>
+        <v>132532684</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582221</v>
+        <v>582295</v>
       </c>
       <c r="R3" t="n">
-        <v>7043494</v>
+        <v>7043428</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 15984-2026 artfynd.xlsx
+++ b/artfynd/A 15984-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132533434</v>
+        <v>132532201</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582221</v>
+        <v>582265</v>
       </c>
       <c r="R2" t="n">
-        <v>7043494</v>
+        <v>7043376</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132532684</v>
+        <v>132532278</v>
       </c>
       <c r="B3" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582295</v>
+        <v>582251</v>
       </c>
       <c r="R3" t="n">
-        <v>7043428</v>
+        <v>7043396</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,11 +892,11 @@
         <v>132532953</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1006,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132533660</v>
+        <v>132533183</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582252</v>
+        <v>582221</v>
       </c>
       <c r="R5" t="n">
-        <v>7043519</v>
+        <v>7043460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,52 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132533328</v>
+        <v>132532684</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>80488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582223</v>
+        <v>582295</v>
       </c>
       <c r="R6" t="n">
-        <v>7043472</v>
+        <v>7043428</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132532995</v>
+        <v>132532869</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1269,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582232</v>
+        <v>582287</v>
       </c>
       <c r="R7" t="n">
-        <v>7043457</v>
+        <v>7043442</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,26 +1310,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132532869</v>
+        <v>132532995</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1381,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582287</v>
+        <v>582232</v>
       </c>
       <c r="R8" t="n">
-        <v>7043442</v>
+        <v>7043457</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,15 +1422,706 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132533660</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>582252</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7043519</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132532470</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>582248</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7043388</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132533129</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>582211</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7043445</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132533259</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>582221</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7043441</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132533434</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>582221</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7043494</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132533328</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>582223</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7043472</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15984-2026 artfynd.xlsx
+++ b/artfynd/A 15984-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132532201</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132532278</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132532953</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132533183</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132532684</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132532869</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132532995</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132533660</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132532470</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132533129</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132533259</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2011,6 +2071,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132533434</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2122,8 +2187,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132533328</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>